--- a/docs/Oficial/estudantes_ficticios.xlsx
+++ b/docs/Oficial/estudantes_ficticios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sharo\Documents\GitHub\sua-parte\docs\Oficial\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frank_o3qkvjc\Documents\GitHub\sua-parte\docs\Oficial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F961A53B-A83E-4CE5-BD2E-1784A6E94ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B04A3B6-1737-46ED-9A2A-90DCE196E9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="644">
   <si>
     <t>id</t>
   </si>
@@ -2013,13 +2013,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2326,43 +2325,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI102"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="36.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2469,39 +2467,39 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="D2" t="s">
         <v>623</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G2" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="H2" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="I2" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="J2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N2" t="s">
         <v>566</v>
@@ -2513,7 +2511,7 @@
         <v>567</v>
       </c>
       <c r="U2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V2" t="s">
         <v>564</v>
@@ -2521,17 +2519,17 @@
       <c r="Y2" t="s">
         <v>564</v>
       </c>
-      <c r="Z2" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>564</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>564</v>
+      <c r="Z2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>1</v>
       </c>
       <c r="AD2" t="b">
         <v>1</v>
@@ -2545,46 +2543,46 @@
       <c r="AG2" t="b">
         <v>1</v>
       </c>
-      <c r="AH2" t="s">
-        <v>564</v>
+      <c r="AH2" t="b">
+        <v>1</v>
       </c>
       <c r="AI2" t="s">
-        <v>580</v>
+        <v>607</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>278</v>
+        <v>637</v>
       </c>
       <c r="D3" t="s">
-        <v>623</v>
+        <v>642</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
         <v>301</v>
       </c>
       <c r="G3" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="H3" t="s">
-        <v>429</v>
+        <v>393</v>
       </c>
       <c r="I3" t="s">
-        <v>523</v>
+        <v>491</v>
       </c>
       <c r="J3" t="s">
         <v>561</v>
       </c>
-      <c r="L3" t="b">
-        <v>1</v>
+      <c r="L3" t="s">
+        <v>565</v>
       </c>
       <c r="N3" t="s">
         <v>566</v>
@@ -2632,39 +2630,42 @@
         <v>1</v>
       </c>
       <c r="AI3" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C4" t="s">
-        <v>249</v>
+        <v>639</v>
       </c>
       <c r="D4" t="s">
-        <v>623</v>
+        <v>642</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
         <v>301</v>
       </c>
       <c r="G4" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="H4" t="s">
-        <v>455</v>
+        <v>466</v>
+      </c>
+      <c r="I4" t="s">
+        <v>554</v>
       </c>
       <c r="J4" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N4" t="s">
         <v>566</v>
@@ -2676,22 +2677,22 @@
         <v>567</v>
       </c>
       <c r="U4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V4" t="s">
-        <v>565</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>564</v>
+        <v>564</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>1</v>
       </c>
       <c r="AC4" t="b">
         <v>1</v>
@@ -2708,43 +2709,43 @@
       <c r="AG4" t="b">
         <v>1</v>
       </c>
-      <c r="AH4" t="s">
-        <v>564</v>
+      <c r="AH4" t="b">
+        <v>1</v>
       </c>
       <c r="AI4" t="s">
-        <v>615</v>
+        <v>591</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>638</v>
       </c>
       <c r="D5" t="s">
-        <v>623</v>
+        <v>642</v>
       </c>
       <c r="E5">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G5" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="H5" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="I5" t="s">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="J5" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L5" t="s">
         <v>565</v>
@@ -2767,17 +2768,17 @@
       <c r="Y5" t="s">
         <v>564</v>
       </c>
-      <c r="Z5" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>564</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>564</v>
+      <c r="Z5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="b">
+        <v>1</v>
       </c>
       <c r="AD5" t="b">
         <v>1</v>
@@ -2791,43 +2792,43 @@
       <c r="AG5" t="b">
         <v>1</v>
       </c>
-      <c r="AH5" t="s">
-        <v>564</v>
+      <c r="AH5" t="b">
+        <v>1</v>
       </c>
       <c r="AI5" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="D6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G6" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="H6" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="I6" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="J6" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L6" t="s">
         <v>565</v>
@@ -2850,17 +2851,17 @@
       <c r="Y6" t="s">
         <v>564</v>
       </c>
-      <c r="Z6" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>564</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>564</v>
+      <c r="Z6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="b">
+        <v>1</v>
       </c>
       <c r="AD6" t="b">
         <v>1</v>
@@ -2874,46 +2875,46 @@
       <c r="AG6" t="b">
         <v>1</v>
       </c>
-      <c r="AH6" t="s">
-        <v>564</v>
+      <c r="AH6" t="b">
+        <v>1</v>
       </c>
       <c r="AI6" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>243</v>
+        <v>282</v>
       </c>
       <c r="D7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
         <v>301</v>
       </c>
       <c r="G7" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="H7" t="s">
-        <v>384</v>
+        <v>440</v>
       </c>
       <c r="I7" t="s">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="J7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N7" t="s">
         <v>566</v>
@@ -2925,7 +2926,7 @@
         <v>567</v>
       </c>
       <c r="U7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V7" t="s">
         <v>564</v>
@@ -2936,11 +2937,11 @@
       <c r="Z7" t="b">
         <v>1</v>
       </c>
-      <c r="AA7" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>564</v>
+      <c r="AA7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>1</v>
       </c>
       <c r="AC7" t="b">
         <v>1</v>
@@ -2961,39 +2962,39 @@
         <v>1</v>
       </c>
       <c r="AI7" t="s">
-        <v>580</v>
+        <v>611</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="D8" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E8">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G8" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="H8" t="s">
-        <v>380</v>
+        <v>416</v>
       </c>
       <c r="I8" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="J8" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="L8" t="s">
         <v>565</v>
@@ -3008,25 +3009,25 @@
         <v>567</v>
       </c>
       <c r="U8" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V8" t="s">
         <v>564</v>
       </c>
-      <c r="Y8" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>564</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>564</v>
+      <c r="Y8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="b">
+        <v>1</v>
       </c>
       <c r="AD8" t="b">
         <v>1</v>
@@ -3040,43 +3041,46 @@
       <c r="AG8" t="b">
         <v>1</v>
       </c>
-      <c r="AH8" t="s">
-        <v>564</v>
+      <c r="AH8" t="b">
+        <v>1</v>
       </c>
       <c r="AI8" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="D9" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E9">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
         <v>301</v>
       </c>
       <c r="G9" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="H9" t="s">
-        <v>418</v>
+        <v>460</v>
+      </c>
+      <c r="I9" t="s">
+        <v>549</v>
       </c>
       <c r="J9" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N9" t="s">
         <v>566</v>
@@ -3088,22 +3092,22 @@
         <v>567</v>
       </c>
       <c r="U9" t="s">
-        <v>564</v>
-      </c>
-      <c r="V9" t="s">
-        <v>564</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>564</v>
+        <v>565</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>1</v>
       </c>
       <c r="AC9" t="b">
         <v>1</v>
@@ -3120,25 +3124,25 @@
       <c r="AG9" t="b">
         <v>1</v>
       </c>
-      <c r="AH9" t="s">
-        <v>564</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>605</v>
+      <c r="AH9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>27977</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="C10" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
       <c r="E10">
         <v>52</v>
@@ -3147,19 +3151,19 @@
         <v>301</v>
       </c>
       <c r="G10" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="H10" t="s">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="I10" t="s">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="J10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L10" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N10" t="s">
         <v>566</v>
@@ -3171,7 +3175,7 @@
         <v>567</v>
       </c>
       <c r="U10" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V10" t="s">
         <v>564</v>
@@ -3182,11 +3186,11 @@
       <c r="Z10" t="b">
         <v>1</v>
       </c>
-      <c r="AA10" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>564</v>
+      <c r="AA10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>1</v>
       </c>
       <c r="AC10" t="b">
         <v>1</v>
@@ -3210,36 +3214,36 @@
         <v>596</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C11" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D11" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
       <c r="E11">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G11" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="H11" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="I11" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="J11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L11" t="s">
         <v>565</v>
@@ -3259,20 +3263,20 @@
       <c r="V11" t="s">
         <v>564</v>
       </c>
-      <c r="Y11" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>564</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>564</v>
+      <c r="Y11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="b">
+        <v>1</v>
       </c>
       <c r="AD11" t="b">
         <v>1</v>
@@ -3286,43 +3290,43 @@
       <c r="AG11" t="b">
         <v>1</v>
       </c>
-      <c r="AH11" t="s">
-        <v>564</v>
+      <c r="AH11" t="b">
+        <v>1</v>
       </c>
       <c r="AI11" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>619</v>
+        <v>570</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G12" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
       <c r="H12" t="s">
-        <v>445</v>
+        <v>409</v>
       </c>
       <c r="I12" t="s">
-        <v>538</v>
+        <v>504</v>
       </c>
       <c r="J12" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L12" t="s">
         <v>565</v>
@@ -3337,7 +3341,7 @@
         <v>567</v>
       </c>
       <c r="U12" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V12" t="s">
         <v>564</v>
@@ -3345,17 +3349,17 @@
       <c r="Y12" t="s">
         <v>564</v>
       </c>
-      <c r="Z12" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>564</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>564</v>
+      <c r="Z12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="b">
+        <v>1</v>
       </c>
       <c r="AD12" t="b">
         <v>1</v>
@@ -3369,40 +3373,43 @@
       <c r="AG12" t="b">
         <v>1</v>
       </c>
-      <c r="AH12" t="s">
-        <v>564</v>
+      <c r="AH12" t="b">
+        <v>1</v>
       </c>
       <c r="AI12" t="s">
-        <v>582</v>
+        <v>501</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>260</v>
+        <v>629</v>
       </c>
       <c r="D13" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G13" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="H13" t="s">
-        <v>450</v>
+        <v>431</v>
+      </c>
+      <c r="I13" t="s">
+        <v>525</v>
       </c>
       <c r="J13" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L13" t="s">
         <v>565</v>
@@ -3417,7 +3424,7 @@
         <v>567</v>
       </c>
       <c r="U13" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V13" t="s">
         <v>564</v>
@@ -3425,17 +3432,17 @@
       <c r="Y13" t="s">
         <v>564</v>
       </c>
-      <c r="Z13" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>564</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>564</v>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="b">
+        <v>1</v>
       </c>
       <c r="AD13" t="b">
         <v>1</v>
@@ -3449,46 +3456,46 @@
       <c r="AG13" t="b">
         <v>1</v>
       </c>
-      <c r="AH13" t="s">
-        <v>564</v>
+      <c r="AH13" t="b">
+        <v>1</v>
       </c>
       <c r="AI13" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>630</v>
       </c>
       <c r="D14" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="E14">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G14" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="H14" t="s">
-        <v>433</v>
+        <v>392</v>
       </c>
       <c r="I14" t="s">
-        <v>527</v>
+        <v>490</v>
       </c>
       <c r="J14" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N14" t="s">
         <v>566</v>
@@ -3500,7 +3507,7 @@
         <v>567</v>
       </c>
       <c r="U14" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V14" t="s">
         <v>564</v>
@@ -3508,17 +3515,17 @@
       <c r="Y14" t="s">
         <v>564</v>
       </c>
-      <c r="Z14" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>564</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>564</v>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>1</v>
       </c>
       <c r="AD14" t="b">
         <v>1</v>
@@ -3532,43 +3539,46 @@
       <c r="AG14" t="b">
         <v>1</v>
       </c>
-      <c r="AH14" t="s">
-        <v>564</v>
+      <c r="AH14" t="b">
+        <v>1</v>
       </c>
       <c r="AI14" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="C15" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G15" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="H15" t="s">
-        <v>377</v>
+        <v>411</v>
+      </c>
+      <c r="I15" t="s">
+        <v>506</v>
       </c>
       <c r="J15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L15" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N15" t="s">
         <v>566</v>
@@ -3583,7 +3593,7 @@
         <v>564</v>
       </c>
       <c r="V15" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y15" t="s">
         <v>564</v>
@@ -3597,8 +3607,8 @@
       <c r="AB15" t="s">
         <v>564</v>
       </c>
-      <c r="AC15" t="b">
-        <v>1</v>
+      <c r="AC15" t="s">
+        <v>564</v>
       </c>
       <c r="AD15" t="b">
         <v>1</v>
@@ -3616,42 +3626,42 @@
         <v>564</v>
       </c>
       <c r="AI15" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="C16" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D16" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
         <v>300</v>
       </c>
       <c r="G16" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H16" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="I16" t="s">
-        <v>524</v>
+        <v>482</v>
       </c>
       <c r="J16" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="L16" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N16" t="s">
         <v>566</v>
@@ -3699,39 +3709,39 @@
         <v>564</v>
       </c>
       <c r="AI16" t="s">
-        <v>608</v>
+        <v>579</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D17" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E17">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>300</v>
       </c>
       <c r="G17" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="H17" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="I17" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="J17" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L17" t="s">
         <v>565</v>
@@ -3782,42 +3792,42 @@
         <v>564</v>
       </c>
       <c r="AI17" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="B18" t="s">
-        <v>135</v>
+        <v>222</v>
       </c>
       <c r="C18" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="D18" t="s">
         <v>619</v>
       </c>
       <c r="E18">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F18" t="s">
         <v>300</v>
       </c>
       <c r="G18" t="s">
-        <v>302</v>
+        <v>369</v>
       </c>
       <c r="H18" t="s">
-        <v>375</v>
+        <v>462</v>
       </c>
       <c r="I18" t="s">
-        <v>475</v>
+        <v>550</v>
       </c>
       <c r="J18" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L18" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N18" t="s">
         <v>566</v>
@@ -3829,7 +3839,7 @@
         <v>567</v>
       </c>
       <c r="U18" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V18" t="s">
         <v>564</v>
@@ -3865,36 +3875,36 @@
         <v>564</v>
       </c>
       <c r="AI18" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="C19" t="s">
-        <v>632</v>
+        <v>285</v>
       </c>
       <c r="D19" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="E19">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
         <v>300</v>
       </c>
       <c r="G19" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="H19" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="I19" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="J19" t="s">
         <v>562</v>
@@ -3948,39 +3958,36 @@
         <v>564</v>
       </c>
       <c r="AI19" t="s">
-        <v>597</v>
+        <v>582</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="C20" t="s">
-        <v>633</v>
+        <v>260</v>
       </c>
       <c r="D20" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="E20">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
         <v>300</v>
       </c>
       <c r="G20" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H20" t="s">
-        <v>473</v>
-      </c>
-      <c r="I20" t="s">
-        <v>557</v>
+        <v>450</v>
       </c>
       <c r="J20" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L20" t="s">
         <v>565</v>
@@ -4031,21 +4038,21 @@
         <v>564</v>
       </c>
       <c r="AI20" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="C21" t="s">
-        <v>633</v>
+        <v>260</v>
       </c>
       <c r="D21" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="E21">
         <v>52</v>
@@ -4054,19 +4061,19 @@
         <v>300</v>
       </c>
       <c r="G21" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H21" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="I21" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="J21" t="s">
         <v>558</v>
       </c>
       <c r="L21" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N21" t="s">
         <v>566</v>
@@ -4117,12 +4124,12 @@
         <v>596</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="C22" t="s">
         <v>632</v>
@@ -4131,7 +4138,7 @@
         <v>641</v>
       </c>
       <c r="E22">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
         <v>300</v>
@@ -4140,10 +4147,10 @@
         <v>353</v>
       </c>
       <c r="H22" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="I22" t="s">
-        <v>530</v>
+        <v>556</v>
       </c>
       <c r="J22" t="s">
         <v>562</v>
@@ -4197,42 +4204,42 @@
         <v>564</v>
       </c>
       <c r="AI22" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="C23" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D23" t="s">
         <v>641</v>
       </c>
       <c r="E23">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
         <v>300</v>
       </c>
       <c r="G23" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H23" t="s">
-        <v>387</v>
+        <v>473</v>
       </c>
       <c r="I23" t="s">
-        <v>486</v>
+        <v>557</v>
       </c>
       <c r="J23" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="L23" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N23" t="s">
         <v>566</v>
@@ -4280,42 +4287,42 @@
         <v>564</v>
       </c>
       <c r="AI23" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="C24" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D24" t="s">
         <v>641</v>
       </c>
       <c r="E24">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="F24" t="s">
         <v>300</v>
       </c>
       <c r="G24" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="H24" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="I24" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="J24" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L24" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N24" t="s">
         <v>566</v>
@@ -4327,7 +4334,7 @@
         <v>567</v>
       </c>
       <c r="U24" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V24" t="s">
         <v>564</v>
@@ -4363,42 +4370,42 @@
         <v>564</v>
       </c>
       <c r="AI24" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="D25" t="s">
         <v>620</v>
       </c>
       <c r="E25">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
         <v>301</v>
       </c>
       <c r="G25" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="H25" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="I25" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="J25" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="L25" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N25" t="s">
         <v>566</v>
@@ -4410,22 +4417,22 @@
         <v>567</v>
       </c>
       <c r="U25" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V25" t="s">
         <v>564</v>
       </c>
-      <c r="Y25" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>564</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>564</v>
+      <c r="Y25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>1</v>
       </c>
       <c r="AC25" t="b">
         <v>1</v>
@@ -4442,46 +4449,46 @@
       <c r="AG25" t="b">
         <v>1</v>
       </c>
-      <c r="AH25" t="s">
-        <v>564</v>
+      <c r="AH25" t="b">
+        <v>1</v>
       </c>
       <c r="AI25" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="C26" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="D26" t="s">
         <v>620</v>
       </c>
       <c r="E26">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="F26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G26" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="H26" t="s">
-        <v>414</v>
+        <v>464</v>
       </c>
       <c r="I26" t="s">
-        <v>509</v>
+        <v>552</v>
       </c>
       <c r="J26" t="s">
         <v>559</v>
       </c>
       <c r="L26" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N26" t="s">
         <v>566</v>
@@ -4493,7 +4500,7 @@
         <v>567</v>
       </c>
       <c r="U26" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V26" t="s">
         <v>564</v>
@@ -4501,8 +4508,8 @@
       <c r="Y26" t="s">
         <v>564</v>
       </c>
-      <c r="Z26" t="b">
-        <v>1</v>
+      <c r="Z26" t="s">
+        <v>564</v>
       </c>
       <c r="AA26" t="s">
         <v>564</v>
@@ -4510,8 +4517,8 @@
       <c r="AB26" t="s">
         <v>564</v>
       </c>
-      <c r="AC26" t="b">
-        <v>1</v>
+      <c r="AC26" t="s">
+        <v>564</v>
       </c>
       <c r="AD26" t="b">
         <v>1</v>
@@ -4525,40 +4532,40 @@
       <c r="AG26" t="b">
         <v>1</v>
       </c>
-      <c r="AH26" t="b">
-        <v>1</v>
+      <c r="AH26" t="s">
+        <v>564</v>
       </c>
       <c r="AI26" t="s">
-        <v>573</v>
+        <v>617</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C27" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="D27" t="s">
         <v>620</v>
       </c>
       <c r="E27">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F27" t="s">
         <v>301</v>
       </c>
       <c r="G27" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="H27" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="I27" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="J27" t="s">
         <v>563</v>
@@ -4612,39 +4619,36 @@
         <v>1</v>
       </c>
       <c r="AI27" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C28" t="s">
-        <v>296</v>
+        <v>257</v>
       </c>
       <c r="D28" t="s">
         <v>620</v>
       </c>
       <c r="E28">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
         <v>300</v>
       </c>
       <c r="G28" t="s">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="H28" t="s">
-        <v>464</v>
-      </c>
-      <c r="I28" t="s">
-        <v>552</v>
+        <v>467</v>
       </c>
       <c r="J28" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L28" t="s">
         <v>565</v>
@@ -4659,10 +4663,10 @@
         <v>567</v>
       </c>
       <c r="U28" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V28" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y28" t="s">
         <v>564</v>
@@ -4695,18 +4699,18 @@
         <v>564</v>
       </c>
       <c r="AI28" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="C29" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="D29" t="s">
         <v>620</v>
@@ -4715,19 +4719,16 @@
         <v>46</v>
       </c>
       <c r="F29" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G29" t="s">
-        <v>364</v>
+        <v>325</v>
       </c>
       <c r="H29" t="s">
-        <v>452</v>
-      </c>
-      <c r="I29" t="s">
-        <v>544</v>
+        <v>401</v>
       </c>
       <c r="J29" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="L29" t="s">
         <v>565</v>
@@ -4742,25 +4743,25 @@
         <v>567</v>
       </c>
       <c r="U29" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V29" t="s">
         <v>564</v>
       </c>
-      <c r="Y29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC29" t="b">
-        <v>1</v>
+      <c r="Y29" t="s">
+        <v>564</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>564</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>564</v>
       </c>
       <c r="AD29" t="b">
         <v>1</v>
@@ -4774,40 +4775,43 @@
       <c r="AG29" t="b">
         <v>1</v>
       </c>
-      <c r="AH29" t="b">
-        <v>1</v>
+      <c r="AH29" t="s">
+        <v>564</v>
       </c>
       <c r="AI29" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>227</v>
+        <v>149</v>
       </c>
       <c r="C30" t="s">
-        <v>257</v>
+        <v>637</v>
       </c>
       <c r="D30" t="s">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="E30">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G30" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="H30" t="s">
-        <v>467</v>
+        <v>389</v>
+      </c>
+      <c r="I30" t="s">
+        <v>487</v>
       </c>
       <c r="J30" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L30" t="s">
         <v>565</v>
@@ -4822,10 +4826,10 @@
         <v>567</v>
       </c>
       <c r="U30" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V30" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y30" t="s">
         <v>564</v>
@@ -4839,8 +4843,8 @@
       <c r="AB30" t="s">
         <v>564</v>
       </c>
-      <c r="AC30" t="s">
-        <v>564</v>
+      <c r="AC30" t="b">
+        <v>1</v>
       </c>
       <c r="AD30" t="b">
         <v>1</v>
@@ -4858,36 +4862,39 @@
         <v>564</v>
       </c>
       <c r="AI30" t="s">
-        <v>618</v>
+        <v>585</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="C31" t="s">
-        <v>257</v>
+        <v>634</v>
       </c>
       <c r="D31" t="s">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="E31">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F31" t="s">
         <v>300</v>
       </c>
       <c r="G31" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="H31" t="s">
-        <v>401</v>
+        <v>438</v>
+      </c>
+      <c r="I31" t="s">
+        <v>532</v>
       </c>
       <c r="J31" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L31" t="s">
         <v>565</v>
@@ -4902,7 +4909,7 @@
         <v>567</v>
       </c>
       <c r="U31" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V31" t="s">
         <v>564</v>
@@ -4938,42 +4945,39 @@
         <v>564</v>
       </c>
       <c r="AI31" t="s">
-        <v>595</v>
+        <v>501</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="C32" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E32">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s">
         <v>301</v>
       </c>
       <c r="G32" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="H32" t="s">
-        <v>385</v>
-      </c>
-      <c r="I32" t="s">
-        <v>484</v>
+        <v>403</v>
       </c>
       <c r="J32" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L32" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N32" t="s">
         <v>566</v>
@@ -4985,7 +4989,7 @@
         <v>567</v>
       </c>
       <c r="U32" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V32" t="s">
         <v>564</v>
@@ -4993,8 +4997,8 @@
       <c r="Y32" t="s">
         <v>564</v>
       </c>
-      <c r="Z32" t="b">
-        <v>1</v>
+      <c r="Z32" t="s">
+        <v>564</v>
       </c>
       <c r="AA32" t="s">
         <v>564</v>
@@ -5017,46 +5021,46 @@
       <c r="AG32" t="b">
         <v>1</v>
       </c>
-      <c r="AH32" t="b">
-        <v>1</v>
+      <c r="AH32" t="s">
+        <v>564</v>
       </c>
       <c r="AI32" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="C33" t="s">
-        <v>635</v>
+        <v>241</v>
       </c>
       <c r="D33" t="s">
-        <v>642</v>
+        <v>622</v>
       </c>
       <c r="E33">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
         <v>300</v>
       </c>
       <c r="G33" t="s">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="H33" t="s">
-        <v>437</v>
+        <v>381</v>
       </c>
       <c r="I33" t="s">
-        <v>531</v>
+        <v>480</v>
       </c>
       <c r="J33" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L33" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N33" t="s">
         <v>566</v>
@@ -5104,42 +5108,42 @@
         <v>564</v>
       </c>
       <c r="AI33" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
-        <v>637</v>
+        <v>236</v>
       </c>
       <c r="D34" t="s">
-        <v>642</v>
+        <v>569</v>
       </c>
       <c r="E34">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
         <v>301</v>
       </c>
       <c r="G34" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="H34" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="I34" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="J34" t="s">
-        <v>561</v>
-      </c>
-      <c r="L34" t="b">
-        <v>1</v>
+        <v>559</v>
+      </c>
+      <c r="L34" t="s">
+        <v>565</v>
       </c>
       <c r="N34" t="s">
         <v>566</v>
@@ -5151,7 +5155,7 @@
         <v>567</v>
       </c>
       <c r="U34" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V34" t="s">
         <v>564</v>
@@ -5162,11 +5166,11 @@
       <c r="Z34" t="b">
         <v>1</v>
       </c>
-      <c r="AA34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB34" t="b">
-        <v>1</v>
+      <c r="AA34" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>564</v>
       </c>
       <c r="AC34" t="b">
         <v>1</v>
@@ -5187,39 +5191,36 @@
         <v>1</v>
       </c>
       <c r="AI34" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>149</v>
+        <v>228</v>
       </c>
       <c r="C35" t="s">
-        <v>637</v>
+        <v>246</v>
       </c>
       <c r="D35" t="s">
-        <v>642</v>
+        <v>569</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F35" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G35" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H35" t="s">
-        <v>389</v>
-      </c>
-      <c r="I35" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="J35" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L35" t="s">
         <v>565</v>
@@ -5234,7 +5235,7 @@
         <v>567</v>
       </c>
       <c r="U35" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V35" t="s">
         <v>564</v>
@@ -5251,8 +5252,8 @@
       <c r="AB35" t="s">
         <v>564</v>
       </c>
-      <c r="AC35" t="b">
-        <v>1</v>
+      <c r="AC35" t="s">
+        <v>564</v>
       </c>
       <c r="AD35" t="b">
         <v>1</v>
@@ -5270,42 +5271,42 @@
         <v>564</v>
       </c>
       <c r="AI35" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="C36" t="s">
-        <v>639</v>
+        <v>236</v>
       </c>
       <c r="D36" t="s">
-        <v>642</v>
+        <v>569</v>
       </c>
       <c r="E36">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
         <v>301</v>
       </c>
       <c r="G36" t="s">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="H36" t="s">
-        <v>466</v>
+        <v>376</v>
       </c>
       <c r="I36" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="J36" t="s">
-        <v>563</v>
-      </c>
-      <c r="L36" t="b">
-        <v>1</v>
+        <v>559</v>
+      </c>
+      <c r="L36" t="s">
+        <v>565</v>
       </c>
       <c r="N36" t="s">
         <v>566</v>
@@ -5322,17 +5323,17 @@
       <c r="V36" t="s">
         <v>564</v>
       </c>
-      <c r="Y36" t="b">
-        <v>1</v>
+      <c r="Y36" t="s">
+        <v>564</v>
       </c>
       <c r="Z36" t="b">
         <v>1</v>
       </c>
-      <c r="AA36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB36" t="b">
-        <v>1</v>
+      <c r="AA36" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>564</v>
       </c>
       <c r="AC36" t="b">
         <v>1</v>
@@ -5353,42 +5354,42 @@
         <v>1</v>
       </c>
       <c r="AI36" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="C37" t="s">
-        <v>638</v>
+        <v>258</v>
       </c>
       <c r="D37" t="s">
-        <v>642</v>
+        <v>569</v>
       </c>
       <c r="E37">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="F37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G37" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="H37" t="s">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="I37" t="s">
-        <v>485</v>
+        <v>539</v>
       </c>
       <c r="J37" t="s">
-        <v>561</v>
-      </c>
-      <c r="L37" t="b">
-        <v>1</v>
+        <v>562</v>
+      </c>
+      <c r="L37" t="s">
+        <v>565</v>
       </c>
       <c r="N37" t="s">
         <v>566</v>
@@ -5408,17 +5409,17 @@
       <c r="Y37" t="s">
         <v>564</v>
       </c>
-      <c r="Z37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC37" t="b">
-        <v>1</v>
+      <c r="Z37" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>564</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>564</v>
       </c>
       <c r="AD37" t="b">
         <v>1</v>
@@ -5432,43 +5433,43 @@
       <c r="AG37" t="b">
         <v>1</v>
       </c>
-      <c r="AH37" t="b">
-        <v>1</v>
+      <c r="AH37" t="s">
+        <v>564</v>
       </c>
       <c r="AI37" t="s">
-        <v>582</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s">
-        <v>634</v>
+        <v>254</v>
       </c>
       <c r="D38" t="s">
-        <v>642</v>
+        <v>570</v>
       </c>
       <c r="E38">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G38" t="s">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="H38" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="I38" t="s">
-        <v>532</v>
+        <v>495</v>
       </c>
       <c r="J38" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="L38" t="s">
         <v>565</v>
@@ -5483,7 +5484,7 @@
         <v>567</v>
       </c>
       <c r="U38" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V38" t="s">
         <v>564</v>
@@ -5491,8 +5492,8 @@
       <c r="Y38" t="s">
         <v>564</v>
       </c>
-      <c r="Z38" t="s">
-        <v>564</v>
+      <c r="Z38" t="b">
+        <v>1</v>
       </c>
       <c r="AA38" t="s">
         <v>564</v>
@@ -5500,8 +5501,8 @@
       <c r="AB38" t="s">
         <v>564</v>
       </c>
-      <c r="AC38" t="s">
-        <v>564</v>
+      <c r="AC38" t="b">
+        <v>1</v>
       </c>
       <c r="AD38" t="b">
         <v>1</v>
@@ -5515,46 +5516,46 @@
       <c r="AG38" t="b">
         <v>1</v>
       </c>
-      <c r="AH38" t="s">
-        <v>564</v>
+      <c r="AH38" t="b">
+        <v>1</v>
       </c>
       <c r="AI38" t="s">
-        <v>501</v>
+        <v>592</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C39" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="D39" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E39">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F39" t="s">
         <v>300</v>
       </c>
       <c r="G39" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="H39" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="I39" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="J39" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L39" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N39" t="s">
         <v>566</v>
@@ -5566,10 +5567,10 @@
         <v>567</v>
       </c>
       <c r="U39" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V39" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y39" t="s">
         <v>564</v>
@@ -5602,36 +5603,39 @@
         <v>564</v>
       </c>
       <c r="AI39" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>625</v>
       </c>
       <c r="D40" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="E40">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G40" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="H40" t="s">
-        <v>403</v>
+        <v>419</v>
+      </c>
+      <c r="I40" t="s">
+        <v>513</v>
       </c>
       <c r="J40" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L40" t="s">
         <v>565</v>
@@ -5646,7 +5650,7 @@
         <v>567</v>
       </c>
       <c r="U40" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V40" t="s">
         <v>564</v>
@@ -5663,8 +5667,8 @@
       <c r="AB40" t="s">
         <v>564</v>
       </c>
-      <c r="AC40" t="b">
-        <v>1</v>
+      <c r="AC40" t="s">
+        <v>564</v>
       </c>
       <c r="AD40" t="b">
         <v>1</v>
@@ -5682,21 +5686,21 @@
         <v>564</v>
       </c>
       <c r="AI40" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C41" t="s">
-        <v>241</v>
+        <v>625</v>
       </c>
       <c r="D41" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="E41">
         <v>18</v>
@@ -5705,16 +5709,16 @@
         <v>300</v>
       </c>
       <c r="G41" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="H41" t="s">
-        <v>381</v>
+        <v>435</v>
       </c>
       <c r="I41" t="s">
-        <v>480</v>
+        <v>529</v>
       </c>
       <c r="J41" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L41" t="s">
         <v>565</v>
@@ -5729,7 +5733,7 @@
         <v>567</v>
       </c>
       <c r="U41" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V41" t="s">
         <v>564</v>
@@ -5768,39 +5772,39 @@
         <v>578</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C42" t="s">
-        <v>241</v>
+        <v>628</v>
       </c>
       <c r="D42" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="E42">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F42" t="s">
         <v>300</v>
       </c>
       <c r="G42" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="H42" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="I42" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="J42" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="L42" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N42" t="s">
         <v>566</v>
@@ -5812,7 +5816,7 @@
         <v>567</v>
       </c>
       <c r="U42" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V42" t="s">
         <v>564</v>
@@ -5848,42 +5852,42 @@
         <v>564</v>
       </c>
       <c r="AI42" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="C43" t="s">
-        <v>269</v>
+        <v>626</v>
       </c>
       <c r="D43" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="E43">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="F43" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G43" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="H43" t="s">
-        <v>463</v>
+        <v>407</v>
       </c>
       <c r="I43" t="s">
-        <v>551</v>
+        <v>502</v>
       </c>
       <c r="J43" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L43" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N43" t="s">
         <v>566</v>
@@ -5912,8 +5916,8 @@
       <c r="AB43" t="s">
         <v>564</v>
       </c>
-      <c r="AC43" t="b">
-        <v>1</v>
+      <c r="AC43" t="s">
+        <v>564</v>
       </c>
       <c r="AD43" t="b">
         <v>1</v>
@@ -5931,42 +5935,42 @@
         <v>564</v>
       </c>
       <c r="AI43" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D44" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E44">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F44" t="s">
         <v>301</v>
       </c>
       <c r="G44" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="H44" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="I44" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="J44" t="s">
-        <v>561</v>
-      </c>
-      <c r="L44" t="b">
-        <v>1</v>
+        <v>558</v>
+      </c>
+      <c r="L44" t="s">
+        <v>565</v>
       </c>
       <c r="N44" t="s">
         <v>566</v>
@@ -5986,14 +5990,14 @@
       <c r="Y44" t="s">
         <v>564</v>
       </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB44" t="b">
-        <v>1</v>
+      <c r="Z44" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>564</v>
       </c>
       <c r="AC44" t="b">
         <v>1</v>
@@ -6010,46 +6014,46 @@
       <c r="AG44" t="b">
         <v>1</v>
       </c>
-      <c r="AH44" t="b">
-        <v>1</v>
+      <c r="AH44" t="s">
+        <v>564</v>
       </c>
       <c r="AI44" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C45" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="D45" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E45">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F45" t="s">
         <v>301</v>
       </c>
       <c r="G45" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="H45" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="I45" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="J45" t="s">
-        <v>561</v>
-      </c>
-      <c r="L45" t="b">
-        <v>1</v>
+        <v>562</v>
+      </c>
+      <c r="L45" t="s">
+        <v>565</v>
       </c>
       <c r="N45" t="s">
         <v>566</v>
@@ -6061,10 +6065,10 @@
         <v>567</v>
       </c>
       <c r="U45" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V45" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y45" t="s">
         <v>564</v>
@@ -6072,11 +6076,11 @@
       <c r="Z45" t="b">
         <v>1</v>
       </c>
-      <c r="AA45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB45" t="b">
-        <v>1</v>
+      <c r="AA45" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>564</v>
       </c>
       <c r="AC45" t="b">
         <v>1</v>
@@ -6097,42 +6101,42 @@
         <v>1</v>
       </c>
       <c r="AI45" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="C46" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="D46" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E46">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F46" t="s">
         <v>300</v>
       </c>
       <c r="G46" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="H46" t="s">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="I46" t="s">
-        <v>528</v>
+        <v>493</v>
       </c>
       <c r="J46" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="L46" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N46" t="s">
         <v>566</v>
@@ -6144,10 +6148,10 @@
         <v>567</v>
       </c>
       <c r="U46" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V46" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y46" t="s">
         <v>564</v>
@@ -6180,42 +6184,42 @@
         <v>564</v>
       </c>
       <c r="AI46" t="s">
-        <v>609</v>
+        <v>590</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C47" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D47" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E47">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F47" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G47" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H47" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="I47" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="J47" t="s">
-        <v>563</v>
-      </c>
-      <c r="L47" t="b">
-        <v>1</v>
+        <v>558</v>
+      </c>
+      <c r="L47" t="s">
+        <v>565</v>
       </c>
       <c r="N47" t="s">
         <v>566</v>
@@ -6232,20 +6236,20 @@
       <c r="V47" t="s">
         <v>564</v>
       </c>
-      <c r="Y47" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC47" t="b">
-        <v>1</v>
+      <c r="Y47" t="s">
+        <v>564</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>564</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>564</v>
       </c>
       <c r="AD47" t="b">
         <v>1</v>
@@ -6259,46 +6263,46 @@
       <c r="AG47" t="b">
         <v>1</v>
       </c>
-      <c r="AH47" t="b">
-        <v>1</v>
+      <c r="AH47" t="s">
+        <v>564</v>
       </c>
       <c r="AI47" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>220</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="D48" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E48">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F48" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G48" t="s">
-        <v>356</v>
+        <v>305</v>
       </c>
       <c r="H48" t="s">
-        <v>460</v>
+        <v>378</v>
       </c>
       <c r="I48" t="s">
-        <v>549</v>
+        <v>477</v>
       </c>
       <c r="J48" t="s">
-        <v>563</v>
-      </c>
-      <c r="L48" t="b">
-        <v>1</v>
+        <v>558</v>
+      </c>
+      <c r="L48" t="s">
+        <v>565</v>
       </c>
       <c r="N48" t="s">
         <v>566</v>
@@ -6310,25 +6314,25 @@
         <v>567</v>
       </c>
       <c r="U48" t="s">
-        <v>565</v>
-      </c>
-      <c r="V48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC48" t="b">
-        <v>1</v>
+        <v>564</v>
+      </c>
+      <c r="V48" t="s">
+        <v>564</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>564</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>564</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>564</v>
       </c>
       <c r="AD48" t="b">
         <v>1</v>
@@ -6342,46 +6346,43 @@
       <c r="AG48" t="b">
         <v>1</v>
       </c>
-      <c r="AH48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI48" s="4">
-        <v>27977</v>
+      <c r="AH48" t="s">
+        <v>564</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>575</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="D49" t="s">
-        <v>569</v>
+        <v>621</v>
       </c>
       <c r="E49">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G49" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="H49" t="s">
-        <v>420</v>
-      </c>
-      <c r="I49" t="s">
-        <v>514</v>
+        <v>395</v>
       </c>
       <c r="J49" t="s">
-        <v>561</v>
-      </c>
-      <c r="L49" t="b">
-        <v>1</v>
+        <v>560</v>
+      </c>
+      <c r="L49" t="s">
+        <v>565</v>
       </c>
       <c r="N49" t="s">
         <v>566</v>
@@ -6401,17 +6402,17 @@
       <c r="Y49" t="s">
         <v>564</v>
       </c>
-      <c r="Z49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC49" t="b">
-        <v>1</v>
+      <c r="Z49" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>564</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>564</v>
       </c>
       <c r="AD49" t="b">
         <v>1</v>
@@ -6425,43 +6426,43 @@
       <c r="AG49" t="b">
         <v>1</v>
       </c>
-      <c r="AH49" t="b">
-        <v>1</v>
+      <c r="AH49" t="s">
+        <v>564</v>
       </c>
       <c r="AI49" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="C50" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="D50" t="s">
-        <v>569</v>
+        <v>621</v>
       </c>
       <c r="E50">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
         <v>301</v>
       </c>
       <c r="G50" t="s">
-        <v>303</v>
+        <v>358</v>
       </c>
       <c r="H50" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="I50" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="J50" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L50" t="s">
         <v>565</v>
@@ -6476,7 +6477,7 @@
         <v>567</v>
       </c>
       <c r="U50" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V50" t="s">
         <v>564</v>
@@ -6484,8 +6485,8 @@
       <c r="Y50" t="s">
         <v>564</v>
       </c>
-      <c r="Z50" t="b">
-        <v>1</v>
+      <c r="Z50" t="s">
+        <v>564</v>
       </c>
       <c r="AA50" t="s">
         <v>564</v>
@@ -6508,40 +6509,43 @@
       <c r="AG50" t="b">
         <v>1</v>
       </c>
-      <c r="AH50" t="b">
-        <v>1</v>
+      <c r="AH50" t="s">
+        <v>564</v>
       </c>
       <c r="AI50" t="s">
-        <v>579</v>
+        <v>612</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>186</v>
       </c>
       <c r="C51" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D51" t="s">
-        <v>569</v>
+        <v>621</v>
       </c>
       <c r="E51">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F51" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G51" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="H51" t="s">
-        <v>468</v>
+        <v>426</v>
+      </c>
+      <c r="I51" t="s">
+        <v>520</v>
       </c>
       <c r="J51" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L51" t="s">
         <v>565</v>
@@ -6573,8 +6577,8 @@
       <c r="AB51" t="s">
         <v>564</v>
       </c>
-      <c r="AC51" t="s">
-        <v>564</v>
+      <c r="AC51" t="b">
+        <v>1</v>
       </c>
       <c r="AD51" t="b">
         <v>1</v>
@@ -6592,42 +6596,39 @@
         <v>564</v>
       </c>
       <c r="AI51" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>234</v>
       </c>
       <c r="C52" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
       <c r="D52" t="s">
-        <v>569</v>
+        <v>621</v>
       </c>
       <c r="E52">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F52" t="s">
         <v>300</v>
       </c>
       <c r="G52" t="s">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="H52" t="s">
-        <v>379</v>
-      </c>
-      <c r="I52" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="J52" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L52" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N52" t="s">
         <v>566</v>
@@ -6675,42 +6676,42 @@
         <v>564</v>
       </c>
       <c r="AI52" t="s">
-        <v>576</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="C53" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="D53" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E53">
         <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G53" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="H53" t="s">
-        <v>456</v>
+        <v>406</v>
       </c>
       <c r="I53" t="s">
-        <v>546</v>
+        <v>501</v>
       </c>
       <c r="J53" t="s">
         <v>559</v>
       </c>
       <c r="L53" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N53" t="s">
         <v>566</v>
@@ -6730,8 +6731,8 @@
       <c r="Y53" t="s">
         <v>564</v>
       </c>
-      <c r="Z53" t="s">
-        <v>564</v>
+      <c r="Z53" t="b">
+        <v>1</v>
       </c>
       <c r="AA53" t="s">
         <v>564</v>
@@ -6739,8 +6740,8 @@
       <c r="AB53" t="s">
         <v>564</v>
       </c>
-      <c r="AC53" t="s">
-        <v>564</v>
+      <c r="AC53" t="b">
+        <v>1</v>
       </c>
       <c r="AD53" t="b">
         <v>1</v>
@@ -6754,43 +6755,40 @@
       <c r="AG53" t="b">
         <v>1</v>
       </c>
-      <c r="AH53" t="s">
-        <v>564</v>
+      <c r="AH53" t="b">
+        <v>1</v>
       </c>
       <c r="AI53" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="C54" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D54" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E54">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="F54" t="s">
         <v>301</v>
       </c>
       <c r="G54" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="H54" t="s">
-        <v>376</v>
-      </c>
-      <c r="I54" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="J54" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L54" t="s">
         <v>565</v>
@@ -6805,7 +6803,7 @@
         <v>567</v>
       </c>
       <c r="U54" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V54" t="s">
         <v>564</v>
@@ -6813,8 +6811,8 @@
       <c r="Y54" t="s">
         <v>564</v>
       </c>
-      <c r="Z54" t="b">
-        <v>1</v>
+      <c r="Z54" t="s">
+        <v>564</v>
       </c>
       <c r="AA54" t="s">
         <v>564</v>
@@ -6837,43 +6835,40 @@
       <c r="AG54" t="b">
         <v>1</v>
       </c>
-      <c r="AH54" t="b">
-        <v>1</v>
+      <c r="AH54" t="s">
+        <v>564</v>
       </c>
       <c r="AI54" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="D55" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E55">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F55" t="s">
         <v>300</v>
       </c>
       <c r="G55" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="H55" t="s">
-        <v>446</v>
-      </c>
-      <c r="I55" t="s">
-        <v>539</v>
+        <v>388</v>
       </c>
       <c r="J55" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L55" t="s">
         <v>565</v>
@@ -6924,42 +6919,42 @@
         <v>564</v>
       </c>
       <c r="AI55" t="s">
-        <v>613</v>
+        <v>584</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B56" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C56" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D56" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E56">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F56" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G56" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H56" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="I56" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="J56" t="s">
-        <v>563</v>
-      </c>
-      <c r="L56" t="b">
-        <v>1</v>
+        <v>562</v>
+      </c>
+      <c r="L56" t="s">
+        <v>565</v>
       </c>
       <c r="N56" t="s">
         <v>566</v>
@@ -6976,20 +6971,20 @@
       <c r="V56" t="s">
         <v>564</v>
       </c>
-      <c r="Y56" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC56" t="b">
-        <v>1</v>
+      <c r="Y56" t="s">
+        <v>564</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>564</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>564</v>
       </c>
       <c r="AD56" t="b">
         <v>1</v>
@@ -7003,43 +6998,46 @@
       <c r="AG56" t="b">
         <v>1</v>
       </c>
-      <c r="AH56" t="b">
-        <v>1</v>
+      <c r="AH56" t="s">
+        <v>564</v>
       </c>
       <c r="AI56" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="B57" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="C57" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D57" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E57">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F57" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G57" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="H57" t="s">
-        <v>454</v>
+        <v>470</v>
+      </c>
+      <c r="I57" t="s">
+        <v>555</v>
       </c>
       <c r="J57" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L57" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N57" t="s">
         <v>566</v>
@@ -7051,7 +7049,7 @@
         <v>567</v>
       </c>
       <c r="U57" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V57" t="s">
         <v>564</v>
@@ -7068,8 +7066,8 @@
       <c r="AB57" t="s">
         <v>564</v>
       </c>
-      <c r="AC57" t="b">
-        <v>1</v>
+      <c r="AC57" t="s">
+        <v>564</v>
       </c>
       <c r="AD57" t="b">
         <v>1</v>
@@ -7087,42 +7085,42 @@
         <v>564</v>
       </c>
       <c r="AI57" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="B58" t="s">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="C58" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="D58" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E58">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F58" t="s">
         <v>301</v>
       </c>
       <c r="G58" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
       <c r="H58" t="s">
-        <v>441</v>
+        <v>382</v>
       </c>
       <c r="I58" t="s">
-        <v>535</v>
+        <v>481</v>
       </c>
       <c r="J58" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L58" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N58" t="s">
         <v>566</v>
@@ -7134,16 +7132,16 @@
         <v>567</v>
       </c>
       <c r="U58" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V58" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y58" t="s">
         <v>564</v>
       </c>
-      <c r="Z58" t="s">
-        <v>564</v>
+      <c r="Z58" t="b">
+        <v>1</v>
       </c>
       <c r="AA58" t="s">
         <v>564</v>
@@ -7166,46 +7164,46 @@
       <c r="AG58" t="b">
         <v>1</v>
       </c>
-      <c r="AH58" t="s">
-        <v>564</v>
+      <c r="AH58" t="b">
+        <v>1</v>
       </c>
       <c r="AI58" t="s">
-        <v>601</v>
+        <v>574</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C59" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="D59" t="s">
-        <v>570</v>
+        <v>623</v>
       </c>
       <c r="E59">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F59" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G59" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="H59" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I59" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J59" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L59" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N59" t="s">
         <v>566</v>
@@ -7217,7 +7215,7 @@
         <v>567</v>
       </c>
       <c r="U59" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V59" t="s">
         <v>564</v>
@@ -7234,8 +7232,8 @@
       <c r="AB59" t="s">
         <v>564</v>
       </c>
-      <c r="AC59" t="b">
-        <v>1</v>
+      <c r="AC59" t="s">
+        <v>564</v>
       </c>
       <c r="AD59" t="b">
         <v>1</v>
@@ -7253,39 +7251,39 @@
         <v>564</v>
       </c>
       <c r="AI59" t="s">
-        <v>614</v>
+        <v>580</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C60" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="D60" t="s">
-        <v>570</v>
+        <v>623</v>
       </c>
       <c r="E60">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F60" t="s">
         <v>301</v>
       </c>
       <c r="G60" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="H60" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="J60" t="s">
         <v>560</v>
       </c>
       <c r="L60" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N60" t="s">
         <v>566</v>
@@ -7297,10 +7295,10 @@
         <v>567</v>
       </c>
       <c r="U60" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V60" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y60" t="s">
         <v>564</v>
@@ -7333,42 +7331,42 @@
         <v>564</v>
       </c>
       <c r="AI60" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B61" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C61" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="D61" t="s">
-        <v>570</v>
+        <v>623</v>
       </c>
       <c r="E61">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
         <v>301</v>
       </c>
       <c r="G61" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="H61" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="I61" t="s">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="J61" t="s">
-        <v>561</v>
-      </c>
-      <c r="L61" t="b">
-        <v>1</v>
+        <v>562</v>
+      </c>
+      <c r="L61" t="s">
+        <v>565</v>
       </c>
       <c r="N61" t="s">
         <v>566</v>
@@ -7391,11 +7389,11 @@
       <c r="Z61" t="b">
         <v>1</v>
       </c>
-      <c r="AA61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB61" t="b">
-        <v>1</v>
+      <c r="AA61" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>564</v>
       </c>
       <c r="AC61" t="b">
         <v>1</v>
@@ -7416,42 +7414,39 @@
         <v>1</v>
       </c>
       <c r="AI61" t="s">
-        <v>501</v>
+        <v>580</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B62" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C62" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D62" t="s">
-        <v>570</v>
+        <v>623</v>
       </c>
       <c r="E62">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F62" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G62" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H62" t="s">
-        <v>424</v>
-      </c>
-      <c r="I62" t="s">
-        <v>518</v>
+        <v>418</v>
       </c>
       <c r="J62" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N62" t="s">
         <v>566</v>
@@ -7463,7 +7458,7 @@
         <v>567</v>
       </c>
       <c r="U62" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V62" t="s">
         <v>564</v>
@@ -7480,8 +7475,8 @@
       <c r="AB62" t="s">
         <v>564</v>
       </c>
-      <c r="AC62" t="s">
-        <v>564</v>
+      <c r="AC62" t="b">
+        <v>1</v>
       </c>
       <c r="AD62" t="b">
         <v>1</v>
@@ -7499,42 +7494,42 @@
         <v>564</v>
       </c>
       <c r="AI62" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C63" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="D63" t="s">
-        <v>570</v>
+        <v>619</v>
       </c>
       <c r="E63">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F63" t="s">
         <v>301</v>
       </c>
       <c r="G63" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="H63" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="I63" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="J63" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L63" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N63" t="s">
         <v>566</v>
@@ -7554,8 +7549,8 @@
       <c r="Y63" t="s">
         <v>564</v>
       </c>
-      <c r="Z63" t="s">
-        <v>564</v>
+      <c r="Z63" t="b">
+        <v>1</v>
       </c>
       <c r="AA63" t="s">
         <v>564</v>
@@ -7578,43 +7573,43 @@
       <c r="AG63" t="b">
         <v>1</v>
       </c>
-      <c r="AH63" t="s">
-        <v>564</v>
+      <c r="AH63" t="b">
+        <v>1</v>
       </c>
       <c r="AI63" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="C64" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="D64" t="s">
-        <v>570</v>
+        <v>619</v>
       </c>
       <c r="E64">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F64" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G64" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="H64" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="I64" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="J64" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L64" t="s">
         <v>565</v>
@@ -7637,8 +7632,8 @@
       <c r="Y64" t="s">
         <v>564</v>
       </c>
-      <c r="Z64" t="b">
-        <v>1</v>
+      <c r="Z64" t="s">
+        <v>564</v>
       </c>
       <c r="AA64" t="s">
         <v>564</v>
@@ -7646,8 +7641,8 @@
       <c r="AB64" t="s">
         <v>564</v>
       </c>
-      <c r="AC64" t="b">
-        <v>1</v>
+      <c r="AC64" t="s">
+        <v>564</v>
       </c>
       <c r="AD64" t="b">
         <v>1</v>
@@ -7661,43 +7656,40 @@
       <c r="AG64" t="b">
         <v>1</v>
       </c>
-      <c r="AH64" t="b">
-        <v>1</v>
+      <c r="AH64" t="s">
+        <v>564</v>
       </c>
       <c r="AI64" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="B65" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="C65" t="s">
-        <v>627</v>
+        <v>237</v>
       </c>
       <c r="D65" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="E65">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G65" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="H65" t="s">
-        <v>413</v>
-      </c>
-      <c r="I65" t="s">
-        <v>508</v>
+        <v>377</v>
       </c>
       <c r="J65" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L65" t="s">
         <v>565</v>
@@ -7712,10 +7704,10 @@
         <v>567</v>
       </c>
       <c r="U65" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V65" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y65" t="s">
         <v>564</v>
@@ -7729,8 +7721,8 @@
       <c r="AB65" t="s">
         <v>564</v>
       </c>
-      <c r="AC65" t="s">
-        <v>564</v>
+      <c r="AC65" t="b">
+        <v>1</v>
       </c>
       <c r="AD65" t="b">
         <v>1</v>
@@ -7748,36 +7740,36 @@
         <v>564</v>
       </c>
       <c r="AI65" t="s">
-        <v>601</v>
+        <v>574</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B66" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C66" t="s">
-        <v>625</v>
+        <v>235</v>
       </c>
       <c r="D66" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="E66">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F66" t="s">
         <v>300</v>
       </c>
       <c r="G66" t="s">
-        <v>342</v>
+        <v>302</v>
       </c>
       <c r="H66" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="I66" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="J66" t="s">
         <v>562</v>
@@ -7795,7 +7787,7 @@
         <v>567</v>
       </c>
       <c r="U66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V66" t="s">
         <v>564</v>
@@ -7831,39 +7823,39 @@
         <v>564</v>
       </c>
       <c r="AI66" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B67" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>625</v>
+        <v>235</v>
       </c>
       <c r="D67" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="E67">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F67" t="s">
         <v>300</v>
       </c>
       <c r="G67" t="s">
-        <v>342</v>
+        <v>302</v>
       </c>
       <c r="H67" t="s">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="I67" t="s">
-        <v>529</v>
+        <v>475</v>
       </c>
       <c r="J67" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="L67" t="s">
         <v>565</v>
@@ -7878,7 +7870,7 @@
         <v>567</v>
       </c>
       <c r="U67" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V67" t="s">
         <v>564</v>
@@ -7914,36 +7906,36 @@
         <v>564</v>
       </c>
       <c r="AI67" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C68" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D68" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E68">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F68" t="s">
         <v>300</v>
       </c>
       <c r="G68" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="H68" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="I68" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="J68" t="s">
         <v>558</v>
@@ -7961,7 +7953,7 @@
         <v>567</v>
       </c>
       <c r="U68" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V68" t="s">
         <v>564</v>
@@ -7997,36 +7989,36 @@
         <v>564</v>
       </c>
       <c r="AI68" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B69" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="C69" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D69" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E69">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="F69" t="s">
         <v>300</v>
       </c>
       <c r="G69" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="H69" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="I69" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="J69" t="s">
         <v>562</v>
@@ -8044,7 +8036,7 @@
         <v>567</v>
       </c>
       <c r="U69" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V69" t="s">
         <v>564</v>
@@ -8080,42 +8072,42 @@
         <v>564</v>
       </c>
       <c r="AI69" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B70" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="C70" t="s">
-        <v>252</v>
+        <v>633</v>
       </c>
       <c r="D70" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="E70">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F70" t="s">
         <v>300</v>
       </c>
       <c r="G70" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="H70" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="I70" t="s">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="J70" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="L70" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N70" t="s">
         <v>566</v>
@@ -8127,10 +8119,10 @@
         <v>567</v>
       </c>
       <c r="U70" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V70" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y70" t="s">
         <v>564</v>
@@ -8163,36 +8155,36 @@
         <v>564</v>
       </c>
       <c r="AI70" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="C71" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="E71">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F71" t="s">
         <v>301</v>
       </c>
       <c r="G71" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="H71" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="I71" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="J71" t="s">
         <v>558</v>
@@ -8210,7 +8202,7 @@
         <v>567</v>
       </c>
       <c r="U71" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V71" t="s">
         <v>564</v>
@@ -8246,39 +8238,39 @@
         <v>564</v>
       </c>
       <c r="AI71" t="s">
-        <v>578</v>
+        <v>597</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="B72" t="s">
-        <v>219</v>
+        <v>174</v>
       </c>
       <c r="C72" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="D72" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="E72">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F72" t="s">
         <v>301</v>
       </c>
       <c r="G72" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="H72" t="s">
-        <v>459</v>
+        <v>414</v>
       </c>
       <c r="I72" t="s">
-        <v>548</v>
+        <v>509</v>
       </c>
       <c r="J72" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="L72" t="s">
         <v>565</v>
@@ -8293,10 +8285,10 @@
         <v>567</v>
       </c>
       <c r="U72" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V72" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y72" t="s">
         <v>564</v>
@@ -8329,42 +8321,42 @@
         <v>1</v>
       </c>
       <c r="AI72" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="C73" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="D73" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="E73">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="F73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G73" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="H73" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="I73" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="J73" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L73" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N73" t="s">
         <v>566</v>
@@ -8384,8 +8376,8 @@
       <c r="Y73" t="s">
         <v>564</v>
       </c>
-      <c r="Z73" t="s">
-        <v>564</v>
+      <c r="Z73" t="b">
+        <v>1</v>
       </c>
       <c r="AA73" t="s">
         <v>564</v>
@@ -8393,8 +8385,8 @@
       <c r="AB73" t="s">
         <v>564</v>
       </c>
-      <c r="AC73" t="s">
-        <v>564</v>
+      <c r="AC73" t="b">
+        <v>1</v>
       </c>
       <c r="AD73" t="b">
         <v>1</v>
@@ -8408,40 +8400,40 @@
       <c r="AG73" t="b">
         <v>1</v>
       </c>
-      <c r="AH73" t="s">
-        <v>564</v>
+      <c r="AH73" t="b">
+        <v>1</v>
       </c>
       <c r="AI73" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="B74" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="C74" t="s">
-        <v>252</v>
+        <v>635</v>
       </c>
       <c r="D74" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="E74">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F74" t="s">
         <v>300</v>
       </c>
       <c r="G74" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="H74" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="I74" t="s">
-        <v>493</v>
+        <v>531</v>
       </c>
       <c r="J74" t="s">
         <v>558</v>
@@ -8459,10 +8451,10 @@
         <v>567</v>
       </c>
       <c r="U74" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V74" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y74" t="s">
         <v>564</v>
@@ -8495,42 +8487,42 @@
         <v>564</v>
       </c>
       <c r="AI74" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="B75" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>253</v>
+        <v>636</v>
       </c>
       <c r="D75" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="E75">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F75" t="s">
         <v>300</v>
       </c>
       <c r="G75" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="H75" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
       <c r="I75" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="J75" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="L75" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N75" t="s">
         <v>566</v>
@@ -8545,7 +8537,7 @@
         <v>564</v>
       </c>
       <c r="V75" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y75" t="s">
         <v>564</v>
@@ -8578,42 +8570,42 @@
         <v>564</v>
       </c>
       <c r="AI75" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B76" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C76" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D76" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E76">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F76" t="s">
         <v>300</v>
       </c>
       <c r="G76" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="H76" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="I76" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="J76" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L76" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N76" t="s">
         <v>566</v>
@@ -8625,7 +8617,7 @@
         <v>567</v>
       </c>
       <c r="U76" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V76" t="s">
         <v>564</v>
@@ -8661,36 +8653,36 @@
         <v>564</v>
       </c>
       <c r="AI76" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="B77" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="C77" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D77" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E77">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F77" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H77" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="I77" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="J77" t="s">
         <v>558</v>
@@ -8725,8 +8717,8 @@
       <c r="AB77" t="s">
         <v>564</v>
       </c>
-      <c r="AC77" t="s">
-        <v>564</v>
+      <c r="AC77" t="b">
+        <v>1</v>
       </c>
       <c r="AD77" t="b">
         <v>1</v>
@@ -8744,39 +8736,39 @@
         <v>564</v>
       </c>
       <c r="AI77" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="B78" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="C78" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="D78" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E78">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F78" t="s">
         <v>300</v>
       </c>
       <c r="G78" t="s">
-        <v>305</v>
+        <v>352</v>
       </c>
       <c r="H78" t="s">
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="I78" t="s">
-        <v>477</v>
+        <v>528</v>
       </c>
       <c r="J78" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L78" t="s">
         <v>565</v>
@@ -8791,7 +8783,7 @@
         <v>567</v>
       </c>
       <c r="U78" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V78" t="s">
         <v>564</v>
@@ -8827,42 +8819,42 @@
         <v>564</v>
       </c>
       <c r="AI78" t="s">
-        <v>575</v>
+        <v>609</v>
       </c>
     </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="C79" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D79" t="s">
-        <v>624</v>
+        <v>569</v>
       </c>
       <c r="E79">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="F79" t="s">
         <v>300</v>
       </c>
       <c r="G79" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="H79" t="s">
-        <v>427</v>
+        <v>379</v>
       </c>
       <c r="I79" t="s">
-        <v>521</v>
+        <v>478</v>
       </c>
       <c r="J79" t="s">
         <v>562</v>
       </c>
       <c r="L79" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N79" t="s">
         <v>566</v>
@@ -8874,10 +8866,10 @@
         <v>567</v>
       </c>
       <c r="U79" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V79" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y79" t="s">
         <v>564</v>
@@ -8910,42 +8902,42 @@
         <v>564</v>
       </c>
       <c r="AI79" t="s">
-        <v>598</v>
+        <v>576</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B80" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C80" t="s">
-        <v>629</v>
+        <v>281</v>
       </c>
       <c r="D80" t="s">
-        <v>643</v>
+        <v>569</v>
       </c>
       <c r="E80">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G80" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="H80" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="I80" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="J80" t="s">
-        <v>561</v>
-      </c>
-      <c r="L80" t="b">
-        <v>1</v>
+        <v>559</v>
+      </c>
+      <c r="L80" t="s">
+        <v>565</v>
       </c>
       <c r="N80" t="s">
         <v>566</v>
@@ -8957,25 +8949,25 @@
         <v>567</v>
       </c>
       <c r="U80" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V80" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y80" t="s">
         <v>564</v>
       </c>
-      <c r="Z80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC80" t="b">
-        <v>1</v>
+      <c r="Z80" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB80" t="s">
+        <v>564</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>564</v>
       </c>
       <c r="AD80" t="b">
         <v>1</v>
@@ -8989,46 +8981,43 @@
       <c r="AG80" t="b">
         <v>1</v>
       </c>
-      <c r="AH80" t="b">
-        <v>1</v>
+      <c r="AH80" t="s">
+        <v>564</v>
       </c>
       <c r="AI80" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="C81" t="s">
-        <v>630</v>
+        <v>291</v>
       </c>
       <c r="D81" t="s">
-        <v>643</v>
+        <v>569</v>
       </c>
       <c r="E81">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F81" t="s">
         <v>301</v>
       </c>
       <c r="G81" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="H81" t="s">
-        <v>392</v>
-      </c>
-      <c r="I81" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="J81" t="s">
-        <v>561</v>
-      </c>
-      <c r="L81" t="b">
-        <v>1</v>
+        <v>560</v>
+      </c>
+      <c r="L81" t="s">
+        <v>565</v>
       </c>
       <c r="N81" t="s">
         <v>566</v>
@@ -9048,14 +9037,14 @@
       <c r="Y81" t="s">
         <v>564</v>
       </c>
-      <c r="Z81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB81" t="b">
-        <v>1</v>
+      <c r="Z81" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>564</v>
+      </c>
+      <c r="AB81" t="s">
+        <v>564</v>
       </c>
       <c r="AC81" t="b">
         <v>1</v>
@@ -9072,40 +9061,43 @@
       <c r="AG81" t="b">
         <v>1</v>
       </c>
-      <c r="AH81" t="b">
-        <v>1</v>
+      <c r="AH81" t="s">
+        <v>564</v>
       </c>
       <c r="AI81" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
     </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="B82" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="C82" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="D82" t="s">
-        <v>621</v>
+        <v>570</v>
       </c>
       <c r="E82">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F82" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G82" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="H82" t="s">
-        <v>395</v>
+        <v>441</v>
+      </c>
+      <c r="I82" t="s">
+        <v>535</v>
       </c>
       <c r="J82" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L82" t="s">
         <v>565</v>
@@ -9120,7 +9112,7 @@
         <v>567</v>
       </c>
       <c r="U82" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V82" t="s">
         <v>564</v>
@@ -9137,8 +9129,8 @@
       <c r="AB82" t="s">
         <v>564</v>
       </c>
-      <c r="AC82" t="s">
-        <v>564</v>
+      <c r="AC82" t="b">
+        <v>1</v>
       </c>
       <c r="AD82" t="b">
         <v>1</v>
@@ -9156,36 +9148,36 @@
         <v>564</v>
       </c>
       <c r="AI82" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
     </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B83" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C83" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D83" t="s">
-        <v>621</v>
+        <v>570</v>
       </c>
       <c r="E83">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F83" t="s">
         <v>301</v>
       </c>
       <c r="G83" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="H83" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="I83" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="J83" t="s">
         <v>558</v>
@@ -9239,39 +9231,36 @@
         <v>564</v>
       </c>
       <c r="AI83" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="B84" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="C84" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D84" t="s">
-        <v>621</v>
+        <v>570</v>
       </c>
       <c r="E84">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F84" t="s">
         <v>301</v>
       </c>
       <c r="G84" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="H84" t="s">
-        <v>426</v>
-      </c>
-      <c r="I84" t="s">
-        <v>520</v>
+        <v>458</v>
       </c>
       <c r="J84" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L84" t="s">
         <v>565</v>
@@ -9286,7 +9275,7 @@
         <v>567</v>
       </c>
       <c r="U84" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V84" t="s">
         <v>564</v>
@@ -9322,42 +9311,42 @@
         <v>564</v>
       </c>
       <c r="AI84" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
     </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D85" t="s">
-        <v>621</v>
+        <v>570</v>
       </c>
       <c r="E85">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="F85" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G85" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="H85" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="I85" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="J85" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L85" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N85" t="s">
         <v>566</v>
@@ -9377,8 +9366,8 @@
       <c r="Y85" t="s">
         <v>564</v>
       </c>
-      <c r="Z85" t="b">
-        <v>1</v>
+      <c r="Z85" t="s">
+        <v>564</v>
       </c>
       <c r="AA85" t="s">
         <v>564</v>
@@ -9386,8 +9375,8 @@
       <c r="AB85" t="s">
         <v>564</v>
       </c>
-      <c r="AC85" t="b">
-        <v>1</v>
+      <c r="AC85" t="s">
+        <v>564</v>
       </c>
       <c r="AD85" t="b">
         <v>1</v>
@@ -9401,40 +9390,43 @@
       <c r="AG85" t="b">
         <v>1</v>
       </c>
-      <c r="AH85" t="b">
-        <v>1</v>
+      <c r="AH85" t="s">
+        <v>564</v>
       </c>
       <c r="AI85" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
     </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="B86" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="C86" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="D86" t="s">
-        <v>621</v>
+        <v>570</v>
       </c>
       <c r="E86">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F86" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G86" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
       <c r="H86" t="s">
-        <v>474</v>
+        <v>439</v>
+      </c>
+      <c r="I86" t="s">
+        <v>533</v>
       </c>
       <c r="J86" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L86" t="s">
         <v>565</v>
@@ -9449,7 +9441,7 @@
         <v>567</v>
       </c>
       <c r="U86" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V86" t="s">
         <v>564</v>
@@ -9466,8 +9458,8 @@
       <c r="AB86" t="s">
         <v>564</v>
       </c>
-      <c r="AC86" t="s">
-        <v>564</v>
+      <c r="AC86" t="b">
+        <v>1</v>
       </c>
       <c r="AD86" t="b">
         <v>1</v>
@@ -9485,42 +9477,42 @@
         <v>564</v>
       </c>
       <c r="AI86" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="C87" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D87" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E87">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="F87" t="s">
         <v>300</v>
       </c>
       <c r="G87" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H87" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="I87" t="s">
-        <v>489</v>
+        <v>517</v>
       </c>
       <c r="J87" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L87" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N87" t="s">
         <v>566</v>
@@ -9535,7 +9527,7 @@
         <v>565</v>
       </c>
       <c r="V87" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y87" t="s">
         <v>564</v>
@@ -9568,36 +9560,36 @@
         <v>564</v>
       </c>
       <c r="AI87" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B88" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D88" t="s">
-        <v>571</v>
+        <v>624</v>
       </c>
       <c r="E88">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G88" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="H88" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="I88" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="J88" t="s">
         <v>559</v>
@@ -9615,16 +9607,16 @@
         <v>567</v>
       </c>
       <c r="U88" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V88" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y88" t="s">
         <v>564</v>
       </c>
-      <c r="Z88" t="b">
-        <v>1</v>
+      <c r="Z88" t="s">
+        <v>564</v>
       </c>
       <c r="AA88" t="s">
         <v>564</v>
@@ -9632,8 +9624,8 @@
       <c r="AB88" t="s">
         <v>564</v>
       </c>
-      <c r="AC88" t="b">
-        <v>1</v>
+      <c r="AC88" t="s">
+        <v>564</v>
       </c>
       <c r="AD88" t="b">
         <v>1</v>
@@ -9647,46 +9639,46 @@
       <c r="AG88" t="b">
         <v>1</v>
       </c>
-      <c r="AH88" t="b">
-        <v>1</v>
+      <c r="AH88" t="s">
+        <v>564</v>
       </c>
       <c r="AI88" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="B89" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="C89" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="D89" t="s">
-        <v>571</v>
+        <v>624</v>
       </c>
       <c r="E89">
         <v>32</v>
       </c>
       <c r="F89" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G89" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="H89" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="I89" t="s">
-        <v>522</v>
+        <v>494</v>
       </c>
       <c r="J89" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L89" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N89" t="s">
         <v>566</v>
@@ -9706,8 +9698,8 @@
       <c r="Y89" t="s">
         <v>564</v>
       </c>
-      <c r="Z89" t="b">
-        <v>1</v>
+      <c r="Z89" t="s">
+        <v>564</v>
       </c>
       <c r="AA89" t="s">
         <v>564</v>
@@ -9715,8 +9707,8 @@
       <c r="AB89" t="s">
         <v>564</v>
       </c>
-      <c r="AC89" t="b">
-        <v>1</v>
+      <c r="AC89" t="s">
+        <v>564</v>
       </c>
       <c r="AD89" t="b">
         <v>1</v>
@@ -9730,40 +9722,43 @@
       <c r="AG89" t="b">
         <v>1</v>
       </c>
-      <c r="AH89" t="b">
-        <v>1</v>
+      <c r="AH89" t="s">
+        <v>564</v>
       </c>
       <c r="AI89" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="B90" t="s">
-        <v>231</v>
+        <v>154</v>
       </c>
       <c r="C90" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D90" t="s">
-        <v>571</v>
+        <v>624</v>
       </c>
       <c r="E90">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F90" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G90" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H90" t="s">
-        <v>471</v>
+        <v>394</v>
+      </c>
+      <c r="I90" t="s">
+        <v>492</v>
       </c>
       <c r="J90" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L90" t="s">
         <v>565</v>
@@ -9795,8 +9790,8 @@
       <c r="AB90" t="s">
         <v>564</v>
       </c>
-      <c r="AC90" t="b">
-        <v>1</v>
+      <c r="AC90" t="s">
+        <v>564</v>
       </c>
       <c r="AD90" t="b">
         <v>1</v>
@@ -9814,42 +9809,42 @@
         <v>564</v>
       </c>
       <c r="AI90" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="C91" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D91" t="s">
-        <v>571</v>
+        <v>624</v>
       </c>
       <c r="E91">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F91" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G91" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="H91" t="s">
-        <v>465</v>
+        <v>427</v>
       </c>
       <c r="I91" t="s">
-        <v>553</v>
+        <v>521</v>
       </c>
       <c r="J91" t="s">
         <v>562</v>
       </c>
       <c r="L91" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N91" t="s">
         <v>566</v>
@@ -9861,16 +9856,16 @@
         <v>567</v>
       </c>
       <c r="U91" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V91" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Y91" t="s">
         <v>564</v>
       </c>
-      <c r="Z91" t="b">
-        <v>1</v>
+      <c r="Z91" t="s">
+        <v>564</v>
       </c>
       <c r="AA91" t="s">
         <v>564</v>
@@ -9878,8 +9873,8 @@
       <c r="AB91" t="s">
         <v>564</v>
       </c>
-      <c r="AC91" t="b">
-        <v>1</v>
+      <c r="AC91" t="s">
+        <v>564</v>
       </c>
       <c r="AD91" t="b">
         <v>1</v>
@@ -9893,43 +9888,46 @@
       <c r="AG91" t="b">
         <v>1</v>
       </c>
-      <c r="AH91" t="b">
-        <v>1</v>
+      <c r="AH91" t="s">
+        <v>564</v>
       </c>
       <c r="AI91" t="s">
-        <v>613</v>
+        <v>598</v>
       </c>
     </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="B92" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="C92" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="D92" t="s">
-        <v>571</v>
+        <v>621</v>
       </c>
       <c r="E92">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="F92" t="s">
         <v>301</v>
       </c>
       <c r="G92" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="H92" t="s">
-        <v>461</v>
+        <v>415</v>
+      </c>
+      <c r="I92" t="s">
+        <v>510</v>
       </c>
       <c r="J92" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L92" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N92" t="s">
         <v>566</v>
@@ -9941,7 +9939,7 @@
         <v>567</v>
       </c>
       <c r="U92" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V92" t="s">
         <v>564</v>
@@ -9949,8 +9947,8 @@
       <c r="Y92" t="s">
         <v>564</v>
       </c>
-      <c r="Z92" t="s">
-        <v>564</v>
+      <c r="Z92" t="b">
+        <v>1</v>
       </c>
       <c r="AA92" t="s">
         <v>564</v>
@@ -9973,40 +9971,43 @@
       <c r="AG92" t="b">
         <v>1</v>
       </c>
-      <c r="AH92" t="s">
-        <v>564</v>
+      <c r="AH92" t="b">
+        <v>1</v>
       </c>
       <c r="AI92" t="s">
-        <v>494</v>
+        <v>602</v>
       </c>
     </row>
-    <row r="93" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B93" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C93" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D93" t="s">
-        <v>568</v>
+        <v>621</v>
       </c>
       <c r="E93">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F93" t="s">
         <v>300</v>
       </c>
       <c r="G93" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H93" t="s">
-        <v>388</v>
+        <v>391</v>
+      </c>
+      <c r="I93" t="s">
+        <v>489</v>
       </c>
       <c r="J93" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L93" t="s">
         <v>565</v>
@@ -10021,7 +10022,7 @@
         <v>567</v>
       </c>
       <c r="U93" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V93" t="s">
         <v>564</v>
@@ -10057,39 +10058,39 @@
         <v>564</v>
       </c>
       <c r="AI93" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
-    <row r="94" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B94" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="C94" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="D94" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E94">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F94" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G94" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="H94" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="I94" t="s">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="J94" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="L94" t="s">
         <v>565</v>
@@ -10112,8 +10113,8 @@
       <c r="Y94" t="s">
         <v>564</v>
       </c>
-      <c r="Z94" t="s">
-        <v>564</v>
+      <c r="Z94" t="b">
+        <v>1</v>
       </c>
       <c r="AA94" t="s">
         <v>564</v>
@@ -10121,8 +10122,8 @@
       <c r="AB94" t="s">
         <v>564</v>
       </c>
-      <c r="AC94" t="s">
-        <v>564</v>
+      <c r="AC94" t="b">
+        <v>1</v>
       </c>
       <c r="AD94" t="b">
         <v>1</v>
@@ -10136,46 +10137,46 @@
       <c r="AG94" t="b">
         <v>1</v>
       </c>
-      <c r="AH94" t="s">
-        <v>564</v>
+      <c r="AH94" t="b">
+        <v>1</v>
       </c>
       <c r="AI94" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
-    <row r="95" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="B95" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D95" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E95">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F95" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G95" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="H95" t="s">
-        <v>400</v>
+        <v>465</v>
       </c>
       <c r="I95" t="s">
-        <v>497</v>
+        <v>553</v>
       </c>
       <c r="J95" t="s">
         <v>562</v>
       </c>
       <c r="L95" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N95" t="s">
         <v>566</v>
@@ -10187,7 +10188,7 @@
         <v>567</v>
       </c>
       <c r="U95" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V95" t="s">
         <v>564</v>
@@ -10195,8 +10196,8 @@
       <c r="Y95" t="s">
         <v>564</v>
       </c>
-      <c r="Z95" t="s">
-        <v>564</v>
+      <c r="Z95" t="b">
+        <v>1</v>
       </c>
       <c r="AA95" t="s">
         <v>564</v>
@@ -10204,8 +10205,8 @@
       <c r="AB95" t="s">
         <v>564</v>
       </c>
-      <c r="AC95" t="s">
-        <v>564</v>
+      <c r="AC95" t="b">
+        <v>1</v>
       </c>
       <c r="AD95" t="b">
         <v>1</v>
@@ -10219,43 +10220,40 @@
       <c r="AG95" t="b">
         <v>1</v>
       </c>
-      <c r="AH95" t="s">
-        <v>564</v>
+      <c r="AH95" t="b">
+        <v>1</v>
       </c>
       <c r="AI95" t="s">
-        <v>594</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="96" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B96" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C96" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D96" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E96">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="F96" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G96" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="H96" t="s">
-        <v>470</v>
-      </c>
-      <c r="I96" t="s">
-        <v>555</v>
+        <v>461</v>
       </c>
       <c r="J96" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L96" t="s">
         <v>565</v>
@@ -10270,7 +10268,7 @@
         <v>567</v>
       </c>
       <c r="U96" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V96" t="s">
         <v>564</v>
@@ -10287,8 +10285,8 @@
       <c r="AB96" t="s">
         <v>564</v>
       </c>
-      <c r="AC96" t="s">
-        <v>564</v>
+      <c r="AC96" t="b">
+        <v>1</v>
       </c>
       <c r="AD96" t="b">
         <v>1</v>
@@ -10306,39 +10304,42 @@
         <v>564</v>
       </c>
       <c r="AI96" t="s">
-        <v>613</v>
+        <v>494</v>
       </c>
     </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="B97" t="s">
-        <v>229</v>
+        <v>160</v>
       </c>
       <c r="C97" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="D97" t="s">
         <v>568</v>
       </c>
       <c r="E97">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F97" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G97" t="s">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="H97" t="s">
-        <v>469</v>
+        <v>400</v>
+      </c>
+      <c r="I97" t="s">
+        <v>497</v>
       </c>
       <c r="J97" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L97" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N97" t="s">
         <v>566</v>
@@ -10367,8 +10368,8 @@
       <c r="AB97" t="s">
         <v>564</v>
       </c>
-      <c r="AC97" t="b">
-        <v>1</v>
+      <c r="AC97" t="s">
+        <v>564</v>
       </c>
       <c r="AD97" t="b">
         <v>1</v>
@@ -10386,39 +10387,39 @@
         <v>564</v>
       </c>
       <c r="AI97" t="s">
-        <v>614</v>
+        <v>594</v>
       </c>
     </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="B98" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C98" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="D98" t="s">
         <v>568</v>
       </c>
       <c r="E98">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="F98" t="s">
         <v>301</v>
       </c>
       <c r="G98" t="s">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="H98" t="s">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="J98" t="s">
         <v>560</v>
       </c>
       <c r="L98" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N98" t="s">
         <v>566</v>
@@ -10466,42 +10467,39 @@
         <v>564</v>
       </c>
       <c r="AI98" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="C99" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="D99" t="s">
         <v>568</v>
       </c>
       <c r="E99">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F99" t="s">
         <v>301</v>
       </c>
       <c r="G99" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="H99" t="s">
-        <v>399</v>
-      </c>
-      <c r="I99" t="s">
-        <v>496</v>
+        <v>442</v>
       </c>
       <c r="J99" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L99" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N99" t="s">
         <v>566</v>
@@ -10513,7 +10511,7 @@
         <v>567</v>
       </c>
       <c r="U99" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V99" t="s">
         <v>564</v>
@@ -10521,8 +10519,8 @@
       <c r="Y99" t="s">
         <v>564</v>
       </c>
-      <c r="Z99" t="b">
-        <v>1</v>
+      <c r="Z99" t="s">
+        <v>564</v>
       </c>
       <c r="AA99" t="s">
         <v>564</v>
@@ -10545,46 +10543,46 @@
       <c r="AG99" t="b">
         <v>1</v>
       </c>
-      <c r="AH99" t="b">
-        <v>1</v>
+      <c r="AH99" t="s">
+        <v>564</v>
       </c>
       <c r="AI99" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
     </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.35">
-      <c r="A100" s="3" t="s">
-        <v>107</v>
+    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>59</v>
       </c>
       <c r="B100" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="C100" t="s">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="D100" t="s">
         <v>568</v>
       </c>
       <c r="E100">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F100" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G100" t="s">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="H100" t="s">
-        <v>447</v>
+        <v>399</v>
       </c>
       <c r="I100" t="s">
-        <v>540</v>
+        <v>496</v>
       </c>
       <c r="J100" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="L100" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N100" t="s">
         <v>566</v>
@@ -10596,7 +10594,7 @@
         <v>567</v>
       </c>
       <c r="U100" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="V100" t="s">
         <v>564</v>
@@ -10604,8 +10602,8 @@
       <c r="Y100" t="s">
         <v>564</v>
       </c>
-      <c r="Z100" t="s">
-        <v>564</v>
+      <c r="Z100" t="b">
+        <v>1</v>
       </c>
       <c r="AA100" t="s">
         <v>564</v>
@@ -10613,8 +10611,8 @@
       <c r="AB100" t="s">
         <v>564</v>
       </c>
-      <c r="AC100" t="s">
-        <v>564</v>
+      <c r="AC100" t="b">
+        <v>1</v>
       </c>
       <c r="AD100" t="b">
         <v>1</v>
@@ -10628,43 +10626,43 @@
       <c r="AG100" t="b">
         <v>1</v>
       </c>
-      <c r="AH100" t="s">
-        <v>564</v>
+      <c r="AH100" t="b">
+        <v>1</v>
       </c>
       <c r="AI100" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="B101" t="s">
-        <v>142</v>
+        <v>207</v>
       </c>
       <c r="C101" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="D101" t="s">
         <v>568</v>
       </c>
       <c r="E101">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F101" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G101" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="H101" t="s">
-        <v>382</v>
+        <v>447</v>
       </c>
       <c r="I101" t="s">
-        <v>481</v>
+        <v>540</v>
       </c>
       <c r="J101" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L101" t="s">
         <v>565</v>
@@ -10679,16 +10677,16 @@
         <v>567</v>
       </c>
       <c r="U101" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="V101" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y101" t="s">
         <v>564</v>
       </c>
-      <c r="Z101" t="b">
-        <v>1</v>
+      <c r="Z101" t="s">
+        <v>564</v>
       </c>
       <c r="AA101" t="s">
         <v>564</v>
@@ -10696,8 +10694,8 @@
       <c r="AB101" t="s">
         <v>564</v>
       </c>
-      <c r="AC101" t="b">
-        <v>1</v>
+      <c r="AC101" t="s">
+        <v>564</v>
       </c>
       <c r="AD101" t="b">
         <v>1</v>
@@ -10711,20 +10709,20 @@
       <c r="AG101" t="b">
         <v>1</v>
       </c>
-      <c r="AH101" t="b">
-        <v>1</v>
+      <c r="AH101" t="s">
+        <v>564</v>
       </c>
       <c r="AI101" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="L102" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AI101" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI101">
-      <sortCondition ref="D1:D101"/>
+      <sortCondition descending="1" ref="L1:L101"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
